--- a/modelo_dados_portfolio.xlsx
+++ b/modelo_dados_portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43224bd983aae2d7/Dout_FUC/01-Disciplinas/04-2026-HANDS ON ARTIGOS TECNOLÓGICOS/05-Artigo-Trabalho final/01-Tentativa 01 - Artigo e código para streamlite/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eliez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_BAB1AB86B12E458344A5BF230535EAB3CD3E6116" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B5F193D-8D6B-48E0-AFC8-83E376B2588C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED3ADBB-5514-46C3-8D8B-BF377E171FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38" yWindow="-13636" windowWidth="24268" windowHeight="13022" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38" yWindow="-13636" windowWidth="24268" windowHeight="13022" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criterios" sheetId="1" r:id="rId1"/>
@@ -18,20 +18,7 @@
     <sheet name="Projetos" sheetId="3" r:id="rId3"/>
     <sheet name="Instrucoes" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -59,33 +46,21 @@
     <t>s_gaussiana</t>
   </si>
   <si>
-    <t>VPL (R$ mil)</t>
-  </si>
-  <si>
     <t>max</t>
   </si>
   <si>
     <t>Tipo 5 - Critério Linear com Indiferença (V-Shape with Indifference)</t>
   </si>
   <si>
-    <t>Alinhamento Estratégico (1-5)</t>
-  </si>
-  <si>
     <t>Tipo 3 - Critério Linear (V-Shape)</t>
   </si>
   <si>
-    <t>Risco de Execução (1-5)</t>
-  </si>
-  <si>
     <t>min</t>
   </si>
   <si>
     <t>Tipo 1 - Critério Usual</t>
   </si>
   <si>
-    <t>Impacto ESG (1-5)</t>
-  </si>
-  <si>
     <t>Tipo 2 - Quasi-Critério (U-Shape)</t>
   </si>
   <si>
@@ -104,36 +79,12 @@
     <t>Obrigatorio</t>
   </si>
   <si>
-    <t>ERP Cloud</t>
-  </si>
-  <si>
     <t>não</t>
   </si>
   <si>
-    <t>Nova Linha de Produção</t>
-  </si>
-  <si>
-    <t>Expansão Nordeste</t>
-  </si>
-  <si>
-    <t>Programa ESG</t>
-  </si>
-  <si>
     <t>sim</t>
   </si>
   <si>
-    <t>Automação Logística</t>
-  </si>
-  <si>
-    <t>CRM Comercial</t>
-  </si>
-  <si>
-    <t>Eficiência Energética</t>
-  </si>
-  <si>
-    <t>Data Analytics</t>
-  </si>
-  <si>
     <t>COMO PREENCHER ESTA PLANILHA</t>
   </si>
   <si>
@@ -143,9 +94,6 @@
     <t xml:space="preserve">  • Peso: importância relativa do critério (o app normaliza para somar 1,00).</t>
   </si>
   <si>
-    <t xml:space="preserve">  • Objetivo: 'max' se quanto maior melhor (VPL, alinhamento); 'min' se quanto menor melhor (risco).</t>
-  </si>
-  <si>
     <t xml:space="preserve">  • FuncaoPreferencia: escolha na lista suspensa um dos 6 tipos de Brans, Vincke &amp; Mareschal (1986):</t>
   </si>
   <si>
@@ -167,12 +115,6 @@
     <t xml:space="preserve">      - Tipo 6 - Critério Gaussiano (Gaussian criterion): crescimento suave P = 1 - exp(-d²/2s²). Usa: s_gaussiana.</t>
   </si>
   <si>
-    <t xml:space="preserve">  • q_indiferenca: limiar de indiferença — usado pelos Tipos 2, 4 e 5 (deixe 0 nos demais).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • p_preferencia: limiar de preferência total — usado pelos Tipos 3, 4 e 5 (deixe 0 nos demais).</t>
-  </si>
-  <si>
     <t xml:space="preserve">  • s_gaussiana: ponto de inflexão s — usado apenas pelo Tipo 6 (deixe 0 nos demais).</t>
   </si>
   <si>
@@ -198,13 +140,58 @@
   </si>
   <si>
     <t>Método: PROMETHEE II (ranking) + PROMETHEE V (carteira ótima sob restrição orçamentária).</t>
+  </si>
+  <si>
+    <t>Projeto 01</t>
+  </si>
+  <si>
+    <t>Projeto 02</t>
+  </si>
+  <si>
+    <t>Projeto 03</t>
+  </si>
+  <si>
+    <t>Projeto 04</t>
+  </si>
+  <si>
+    <t>Projeto 05</t>
+  </si>
+  <si>
+    <t>Projeto 06</t>
+  </si>
+  <si>
+    <t>Projeto 07</t>
+  </si>
+  <si>
+    <t>Projeto 08</t>
+  </si>
+  <si>
+    <t>Financeiro - VPL (R$ mil)</t>
+  </si>
+  <si>
+    <t>Alinhamento (1-10)</t>
+  </si>
+  <si>
+    <t>Risco (1-10)</t>
+  </si>
+  <si>
+    <t>Sustentabilidade (1-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Objetivo: 'max' se quanto maior melhor (Financeiro, alinhamento); 'min' se quanto menor melhor (risco).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • q_indiferenca: limiar de indiferença — usado pelos Tipos 4, 8 e 10 (deixe 0 nos demais).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • p_preferencia: limiar de preferência total — usado pelos Tipos 6, 8 e 10 (deixe 0 nos demais).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,24 +204,26 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -277,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -285,6 +274,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -607,125 +597,125 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="9" style="9" customWidth="1"/>
-    <col min="4" max="4" width="73.6640625" customWidth="1"/>
-    <col min="5" max="7" width="18.109375" style="9" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8" style="10" customWidth="1"/>
+    <col min="3" max="3" width="9" style="10" customWidth="1"/>
+    <col min="4" max="4" width="68.109375" style="10" customWidth="1"/>
+    <col min="5" max="7" width="16.77734375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="7">
-        <v>50</v>
-      </c>
-      <c r="F2" s="7">
-        <v>500</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="E2" s="8">
+        <v>100</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1000</v>
+      </c>
+      <c r="G2" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7">
+        <v>48</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="8">
         <v>0</v>
       </c>
-      <c r="F3" s="7">
-        <v>2</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="F3" s="8">
+        <v>4</v>
+      </c>
+      <c r="G3" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="7">
+        <v>49</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="8">
         <v>0</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>0</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7">
+        <v>50</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8">
         <v>0</v>
       </c>
-      <c r="F5" s="7">
-        <v>2</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="F5" s="8">
+        <v>4</v>
+      </c>
+      <c r="G5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -753,32 +743,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -792,222 +782,223 @@
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16" style="9" customWidth="1"/>
-    <col min="5" max="5" width="33.21875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="32.44140625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="24.109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="29.45" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1200</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="7">
-        <v>900</v>
-      </c>
-      <c r="E2" s="7">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2400</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E2" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3">
         <v>4</v>
-      </c>
-      <c r="F2" s="7">
-        <v>3</v>
-      </c>
-      <c r="G2" s="7">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="7">
-        <v>3500</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="7">
-        <v>2200</v>
-      </c>
-      <c r="E3" s="7">
-        <v>5</v>
-      </c>
-      <c r="F3" s="7">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3">
+        <v>7000</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E3" s="3">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3">
         <v>4</v>
-      </c>
-      <c r="G3" s="7">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="7">
-        <v>2800</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1800</v>
-      </c>
-      <c r="E4" s="7">
-        <v>4</v>
-      </c>
-      <c r="F4" s="7">
-        <v>4</v>
-      </c>
-      <c r="G4" s="7">
-        <v>3</v>
+        <v>41</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5600</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E4" s="3">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="7">
-        <v>800</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="7">
-        <v>150</v>
-      </c>
-      <c r="E5" s="7">
-        <v>3</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3">
+        <v>300</v>
+      </c>
+      <c r="E5" s="3">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1500</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1100</v>
-      </c>
-      <c r="E6" s="7">
-        <v>3</v>
-      </c>
-      <c r="F6" s="7">
-        <v>2</v>
-      </c>
-      <c r="G6" s="7">
-        <v>3</v>
+        <v>43</v>
+      </c>
+      <c r="B6" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E6" s="3">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="7">
-        <v>600</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="7">
-        <v>450</v>
-      </c>
-      <c r="E7" s="7">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1200</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3">
+        <v>900</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1</v>
+      <c r="G7" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="7">
-        <v>900</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="7">
-        <v>600</v>
-      </c>
-      <c r="E8" s="7">
-        <v>3</v>
-      </c>
-      <c r="F8" s="7">
-        <v>2</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5</v>
+        <v>45</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="7">
-        <v>700</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="7">
-        <v>500</v>
-      </c>
-      <c r="E9" s="7">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
         <v>4</v>
       </c>
-      <c r="F9" s="7">
-        <v>2</v>
-      </c>
-      <c r="G9" s="7">
-        <v>2</v>
+      <c r="G9" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1021,122 +1012,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.65" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/modelo_dados_portfolio.xlsx
+++ b/modelo_dados_portfolio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eliez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43224bd983aae2d7/Dout_FUC/01-Disciplinas/04-2026-HANDS ON ARTIGOS TECNOLÓGICOS/05-Artigo-Trabalho final/01-Tentativa 01 - Artigo e código para streamlite/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED3ADBB-5514-46C3-8D8B-BF377E171FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{0ED3ADBB-5514-46C3-8D8B-BF377E171FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5414617F-2D63-47BF-9849-41C2DF3A97F9}"/>
   <bookViews>
-    <workbookView xWindow="-38" yWindow="-13636" windowWidth="24268" windowHeight="13022" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38" yWindow="-13636" windowWidth="24268" windowHeight="13022" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criterios" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -274,7 +274,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -598,32 +597,32 @@
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="8" style="10" customWidth="1"/>
-    <col min="3" max="3" width="9" style="10" customWidth="1"/>
-    <col min="4" max="4" width="68.109375" style="10" customWidth="1"/>
-    <col min="5" max="7" width="16.77734375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="8" style="9" customWidth="1"/>
+    <col min="3" max="3" width="9" style="9" customWidth="1"/>
+    <col min="4" max="4" width="68.109375" style="9" customWidth="1"/>
+    <col min="5" max="7" width="16.77734375" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:7" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -631,22 +630,22 @@
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.3</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>100</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>1000</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -654,22 +653,22 @@
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>0.25</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>0</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>4</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -677,22 +676,22 @@
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>0.25</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>0</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>0</v>
       </c>
     </row>
@@ -700,22 +699,22 @@
       <c r="A5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>0.2</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>0</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>4</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -782,15 +781,13 @@
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="2" max="2" width="14" style="9" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="36" style="9" customWidth="1"/>
+    <col min="5" max="7" width="31.21875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -817,22 +814,22 @@
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="7">
         <v>2400</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="7">
         <v>1800</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="7">
         <v>8</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="7">
         <v>6</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="7">
         <v>4</v>
       </c>
     </row>
@@ -840,22 +837,22 @@
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="7">
         <v>7000</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="7">
         <v>4400</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="7">
         <v>10</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="7">
         <v>8</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="7">
         <v>4</v>
       </c>
     </row>
@@ -863,22 +860,22 @@
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="7">
         <v>5600</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="7">
         <v>3600</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="7">
         <v>8</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="7">
         <v>8</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="7">
         <v>6</v>
       </c>
     </row>
@@ -886,22 +883,22 @@
       <c r="A5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="7">
         <v>1600</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="7">
         <v>300</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="7">
         <v>6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="7">
         <v>2</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="7">
         <v>10</v>
       </c>
     </row>
@@ -909,22 +906,22 @@
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="7">
         <v>3000</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="7">
         <v>2200</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="7">
         <v>6</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="7">
         <v>4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="7">
         <v>6</v>
       </c>
     </row>
@@ -932,22 +929,22 @@
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="7">
         <v>1200</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="7">
         <v>900</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="7">
         <v>4</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="7">
         <v>2</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="7">
         <v>2</v>
       </c>
     </row>
@@ -955,22 +952,22 @@
       <c r="A8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="7">
         <v>1800</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="7">
         <v>1200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="7">
         <v>6</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="7">
         <v>4</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="7">
         <v>10</v>
       </c>
     </row>
@@ -978,22 +975,22 @@
       <c r="A9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="7">
         <v>1400</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="7">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="7">
         <v>4</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="7">
         <v>4</v>
       </c>
     </row>
@@ -1012,121 +1009,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.65" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
+      <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+      <c r="A23" s="4"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
     </row>
